--- a/tinHelm/excel/4_DiceRule.xlsx
+++ b/tinHelm/excel/4_DiceRule.xlsx
@@ -4,18 +4,17 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16890" windowHeight="9540"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="4_DiceRule" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Sheet2" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -29,7 +28,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>numNeed</t>
+    <t>numNeed_ENUM</t>
   </si>
   <si>
     <t>numNeedDes</t>
@@ -617,62 +616,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="1" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
-        <v>40001</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>40002</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>40003</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>40004</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>40005</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>40006</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>